--- a/AAII_Financials/Quarterly/TOVX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TOVX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>TOVX</t>
   </si>
@@ -656,126 +656,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
         <v>300</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F8" s="3" t="s">
         <v>4</v>
       </c>
@@ -809,8 +813,8 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -839,8 +843,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -913,17 +920,20 @@
       <c r="Z9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F10" s="3" t="s">
         <v>4</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E12" s="3">
         <v>400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,52 +1180,55 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>-800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>9200</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1217,11 +1237,11 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1237,8 +1257,11 @@
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,25 +1362,26 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3800</v>
       </c>
-      <c r="G17" s="3">
-        <v>13100</v>
-      </c>
       <c r="H17" s="3">
-        <v>4400</v>
+        <v>3900</v>
       </c>
       <c r="I17" s="3">
         <v>4400</v>
@@ -1363,72 +1390,75 @@
         <v>4400</v>
       </c>
       <c r="K17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L17" s="3">
         <v>4700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7300</v>
-      </c>
-      <c r="R17" s="3">
-        <v>5000</v>
       </c>
       <c r="S17" s="3">
         <v>5000</v>
       </c>
       <c r="T17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="U17" s="3">
         <v>4300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2500</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>2100</v>
       </c>
       <c r="Z17" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-13100</v>
-      </c>
       <c r="H18" s="3">
-        <v>-4400</v>
+        <v>-3900</v>
       </c>
       <c r="I18" s="3">
         <v>-4400</v>
@@ -1437,55 +1467,58 @@
         <v>-4400</v>
       </c>
       <c r="K18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="L18" s="3">
         <v>-4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7300</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-5000</v>
       </c>
       <c r="S18" s="3">
         <v>-5000</v>
       </c>
       <c r="T18" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="U18" s="3">
         <v>-4300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-2100</v>
       </c>
       <c r="Z18" s="3">
         <v>-2100</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3">
+        <v>-2100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1557,14 +1591,14 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1586,25 +1620,28 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-13100</v>
-      </c>
       <c r="H21" s="3">
-        <v>-4400</v>
+        <v>-3900</v>
       </c>
       <c r="I21" s="3">
         <v>-4400</v>
@@ -1613,55 +1650,58 @@
         <v>-4400</v>
       </c>
       <c r="K21" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="L21" s="3">
         <v>-4700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5200</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-5800</v>
       </c>
       <c r="N21" s="3">
         <v>-5800</v>
       </c>
       <c r="O21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="P21" s="3">
         <v>-5400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-2100</v>
       </c>
       <c r="Z21" s="3">
         <v>-2100</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3">
+        <v>-2100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1704,8 +1744,8 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1734,82 +1774,88 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2000</v>
+        <v>-3200</v>
       </c>
       <c r="E23" s="3">
         <v>-2000</v>
       </c>
       <c r="F23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G23" s="3">
         <v>-4400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-2100</v>
       </c>
       <c r="Z23" s="3">
         <v>-2100</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3">
+        <v>-2100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1840,27 +1886,27 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>4</v>
       </c>
@@ -1870,8 +1916,8 @@
       <c r="V24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -1882,8 +1928,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2000</v>
+        <v>-3200</v>
       </c>
       <c r="E26" s="3">
         <v>-2000</v>
       </c>
       <c r="F26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G26" s="3">
         <v>-4400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-2100</v>
       </c>
       <c r="Z26" s="3">
         <v>-2100</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3">
+        <v>-2100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2445,14 +2515,14 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2474,82 +2544,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2000</v>
+        <v>-3200</v>
       </c>
       <c r="E33" s="3">
         <v>-2000</v>
       </c>
       <c r="F33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G33" s="3">
         <v>-4400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2000</v>
+        <v>-3200</v>
       </c>
       <c r="E35" s="3">
         <v>-2000</v>
       </c>
       <c r="F35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G35" s="3">
         <v>-4400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E41" s="3">
         <v>14400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>41800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>50500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>52300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>56700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>67300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>72100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>74300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>76900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,8 +3069,11 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2988,25 +3081,25 @@
         <v>1800</v>
       </c>
       <c r="E43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F43" s="3">
         <v>3800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2000</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1900</v>
       </c>
       <c r="L43" s="3">
         <v>1900</v>
@@ -3015,13 +3108,13 @@
         <v>1900</v>
       </c>
       <c r="N43" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O43" s="3">
         <v>1600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
-      </c>
-      <c r="P43" s="3">
-        <v>200</v>
       </c>
       <c r="Q43" s="3">
         <v>200</v>
@@ -3030,14 +3123,14 @@
         <v>200</v>
       </c>
       <c r="S43" s="3">
+        <v>200</v>
+      </c>
+      <c r="T43" s="3">
         <v>300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1700</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
@@ -3048,13 +3141,16 @@
         <v>0</v>
       </c>
       <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
         <v>500</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3097,8 +3193,8 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3127,13 +3223,16 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>100</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -3141,142 +3240,148 @@
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
       </c>
       <c r="J45" s="3">
         <v>400</v>
       </c>
       <c r="K45" s="3">
+        <v>400</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E46" s="3">
         <v>16800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>27400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>34800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>38000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>40300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>45500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>52700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>54900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>59600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>68900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>73600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>75600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>78600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3319,8 +3424,8 @@
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3349,82 +3454,88 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>2200</v>
       </c>
       <c r="N48" s="3">
         <v>2200</v>
       </c>
       <c r="O48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P48" s="3">
         <v>2300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23500</v>
-      </c>
-      <c r="U48" s="3">
-        <v>1500</v>
       </c>
       <c r="V48" s="3">
         <v>1500</v>
       </c>
       <c r="W48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X48" s="3">
         <v>1600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>400</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>500</v>
       </c>
       <c r="Z48" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3450,38 +3561,38 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>1500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5500</v>
-      </c>
-      <c r="O49" s="3">
-        <v>5600</v>
       </c>
       <c r="P49" s="3">
         <v>5600</v>
       </c>
       <c r="Q49" s="3">
+        <v>5600</v>
+      </c>
+      <c r="R49" s="3">
         <v>5500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5800</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3663,7 +3783,7 @@
         <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
@@ -3684,7 +3804,7 @@
         <v>200</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
@@ -3702,7 +3822,7 @@
         <v>100</v>
       </c>
       <c r="U52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>38200</v>
+        <v>34900</v>
       </c>
       <c r="E54" s="3">
         <v>38200</v>
       </c>
       <c r="F54" s="3">
+        <v>38200</v>
+      </c>
+      <c r="G54" s="3">
         <v>30800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>40100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>48700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>55200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>61500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>65400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>67900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>71900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>78700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>82300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>89000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>70400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>75100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>77300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>79100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,99 +4053,103 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>800</v>
       </c>
       <c r="N57" s="3">
         <v>800</v>
       </c>
       <c r="O57" s="3">
+        <v>800</v>
+      </c>
+      <c r="P57" s="3">
         <v>700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1300</v>
-      </c>
-      <c r="W57" s="3">
-        <v>600</v>
       </c>
       <c r="X57" s="3">
         <v>600</v>
       </c>
       <c r="Y57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>600</v>
-      </c>
-      <c r="F58" s="3">
-        <v>700</v>
       </c>
       <c r="G58" s="3">
         <v>700</v>
       </c>
       <c r="H58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I58" s="3">
         <v>600</v>
@@ -4033,7 +4167,7 @@
         <v>600</v>
       </c>
       <c r="N58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="O58" s="3">
         <v>500</v>
@@ -4042,7 +4176,7 @@
         <v>500</v>
       </c>
       <c r="Q58" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="R58" s="3">
         <v>100</v>
@@ -4053,8 +4187,8 @@
       <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
+      <c r="U58" s="3">
+        <v>100</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
@@ -4071,31 +4205,34 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E59" s="3">
         <v>2600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1600</v>
-      </c>
-      <c r="J59" s="3">
-        <v>900</v>
       </c>
       <c r="K59" s="3">
         <v>900</v>
@@ -4107,164 +4244,170 @@
         <v>900</v>
       </c>
       <c r="N59" s="3">
+        <v>900</v>
+      </c>
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1900</v>
-      </c>
-      <c r="W59" s="3">
-        <v>1500</v>
       </c>
       <c r="X59" s="3">
         <v>1500</v>
       </c>
       <c r="Y59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z59" s="3">
         <v>2100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E60" s="3">
         <v>10300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3200</v>
-      </c>
-      <c r="W60" s="3">
-        <v>2100</v>
       </c>
       <c r="X60" s="3">
         <v>2100</v>
       </c>
       <c r="Y60" s="3">
-        <v>3000</v>
+        <v>2100</v>
       </c>
       <c r="Z60" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2100</v>
-      </c>
-      <c r="G61" s="3">
-        <v>2200</v>
       </c>
       <c r="H61" s="3">
         <v>2200</v>
       </c>
       <c r="I61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J61" s="3">
         <v>1000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>200</v>
       </c>
       <c r="R61" s="3">
         <v>200</v>
@@ -4276,7 +4419,7 @@
         <v>200</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -4293,64 +4436,67 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E62" s="3">
         <v>9400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10000</v>
-      </c>
-      <c r="R62" s="3">
-        <v>7200</v>
       </c>
       <c r="S62" s="3">
         <v>7200</v>
       </c>
       <c r="T62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="U62" s="3">
         <v>9800</v>
-      </c>
-      <c r="U62" s="3">
-        <v>1400</v>
       </c>
       <c r="V62" s="3">
         <v>1400</v>
@@ -4359,16 +4505,19 @@
         <v>1400</v>
       </c>
       <c r="X62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E66" s="3">
         <v>22800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15500</v>
-      </c>
-      <c r="N66" s="3">
-        <v>17700</v>
       </c>
       <c r="O66" s="3">
         <v>17700</v>
       </c>
       <c r="P66" s="3">
-        <v>17300</v>
+        <v>17700</v>
       </c>
       <c r="Q66" s="3">
         <v>17300</v>
       </c>
       <c r="R66" s="3">
+        <v>17300</v>
+      </c>
+      <c r="S66" s="3">
         <v>20500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>800</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z66" s="3">
         <v>400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4866,10 +5034,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>1700</v>
-      </c>
-      <c r="L70" s="3">
-        <v>2700</v>
       </c>
       <c r="M70" s="3">
         <v>2700</v>
@@ -4890,7 +5058,7 @@
         <v>2700</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -4908,13 +5076,16 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>15300</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
         <v>15300</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>15300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-364000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-360800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-358700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-356700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-352400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-339300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-335000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-330500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-322800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-314500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-309300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-303800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-300500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-295400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-291000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-285400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-280500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-275600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-271300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-266000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-262700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-259600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-248100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-245000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>15400</v>
+        <v>12200</v>
       </c>
       <c r="E76" s="3">
         <v>15400</v>
       </c>
       <c r="F76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="G76" s="3">
         <v>6700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>31400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>51800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>55400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>61700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>68000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>65400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>73300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>76500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>79600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2000</v>
+        <v>-3200</v>
       </c>
       <c r="E81" s="3">
         <v>-2000</v>
       </c>
       <c r="F81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G81" s="3">
         <v>-4400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5684,10 +5883,13 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,16 +6378,17 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -6175,11 +6396,11 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -6187,27 +6408,27 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -6229,11 +6450,14 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,16 +6607,19 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -6397,11 +6627,11 @@
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -6409,36 +6639,36 @@
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-100</v>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-4300</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -6451,11 +6681,14 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6526,8 +6760,8 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,65 +7021,68 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>3900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>3700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
         <v>-1500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>2100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2700</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-1400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -6844,28 +7090,31 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>74000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
@@ -6873,43 +7122,43 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>4</v>
@@ -6926,78 +7175,84 @@
       <c r="Z101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>70700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2100</v>
       </c>
     </row>
